--- a/data/advisor/qiriness-advisor-conversation-notes-v4.xlsx
+++ b/data/advisor/qiriness-advisor-conversation-notes-v4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnoua\Desktop_backup\APP_DEV\03_Qiriness_Email\Qirines_Email_Automation\data\advisor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5DBC1B-D61F-431C-9259-F7258B45B328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18FA41A-2DCA-4833-9228-3B57BC3157D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9EF54A-957E-4086-91F0-E25A599AA4CE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>#</t>
   </si>
@@ -288,6 +288,16 @@
   </si>
   <si>
     <t>this is another example where the user should be reminded to provide order number in the contact form</t>
+  </si>
+  <si>
+    <t>J'ai des rougeurs persistantes sur les joues. Avez-vous quelque chose pour les atténuer ?
+Conseiller :
+Je comprends, ces rougeurs persistantes peuvent être inconfortables. Pour mieux vous orienter, quelle autre préoccupation souhaitez-vous aussi prendre en compte ?
+Crème Éclat Jour &amp; Nuit - Caresse Active Énergie
+Soins Crèmes Anti-âge Duo Jour &amp; Nuit Temps Sublime</t>
+  </si>
+  <si>
+    <t>Now it asks for preocupation (0</t>
   </si>
 </sst>
 </file>
@@ -645,14 +655,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0839F0E-ACF3-470F-AF33-E9C7CBCC2C78}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34.5703125" customWidth="1"/>
     <col min="3" max="3" width="30.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -663,7 +673,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -674,7 +684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -685,7 +695,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="184.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -695,8 +705,14 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -707,7 +723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="345" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="345" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -718,7 +734,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="390" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="390" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -729,7 +745,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="270" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="270" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -740,7 +756,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="315" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="315" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -751,7 +767,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="225" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="225" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -762,7 +778,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="285" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="285" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -773,7 +789,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -784,7 +800,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="195" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -795,7 +811,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="225" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="225" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -806,7 +822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -817,7 +833,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="330" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="330" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
